--- a/Result/profitability/9945.xlsx
+++ b/Result/profitability/9945.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.49</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9337500000000001</v>
+        <v>1.1125</v>
       </c>
       <c r="N2" t="n">
-        <v>23.8525</v>
+        <v>24.2375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8062499999999999</v>
+        <v>1.0525</v>
       </c>
       <c r="N3" t="n">
-        <v>22.38125</v>
+        <v>21.9325</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.72375</v>
+        <v>1.135</v>
       </c>
       <c r="N4" t="n">
-        <v>20.02</v>
+        <v>20.38375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7912499999999999</v>
+        <v>1.67625</v>
       </c>
       <c r="N5" t="n">
-        <v>17.805</v>
+        <v>18.08</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>-0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.50375</v>
+        <v>0.72375</v>
       </c>
       <c r="N6" t="n">
-        <v>16.56875</v>
+        <v>16.84875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>0.425</v>
+        <v>0.60875</v>
       </c>
       <c r="N7" t="n">
-        <v>15.45875</v>
+        <v>15.98125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.28125</v>
+        <v>0.4975</v>
       </c>
       <c r="N8" t="n">
-        <v>14.85875</v>
+        <v>15.15375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9352,25 +9352,25 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5548</v>
+        <v>-12561</v>
       </c>
       <c r="J71" t="n">
-        <v>7215</v>
+        <v>-10894</v>
       </c>
       <c r="K71" t="n">
-        <v>6222</v>
+        <v>-11886</v>
       </c>
       <c r="L71" t="n">
-        <v>2.28</v>
+        <v>-4.35</v>
       </c>
       <c r="M71" t="n">
-        <v>1.0975</v>
+        <v>0.26875</v>
       </c>
       <c r="N71" t="n">
         <v>26.26375</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -9382,7 +9382,7 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
         <v>0</v>
@@ -9394,10 +9394,10 @@
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>2.84</v>
+        <v>-3.79</v>
       </c>
       <c r="X71" t="n">
-        <v>-5.07142857142857</v>
+        <v>6.767857142857141</v>
       </c>
       <c r="Y71" t="n">
         <v>0.7099999999999973</v>
@@ -9406,10 +9406,10 @@
         <v>0.02935097147581645</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.7399999999999998</v>
+        <v>-5.89</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.4805194805194803</v>
+        <v>-3.824675324675324</v>
       </c>
       <c r="AC71" t="n">
         <v>-2.880000000000003</v>
@@ -9418,10 +9418,10 @@
         <v>-0.103671706263499</v>
       </c>
       <c r="AE71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>1</v>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>EPS成長 / 毛利率衰退</t>
+          <t>EPS衰退 / 毛利率衰退</t>
         </is>
       </c>
       <c r="AK71" t="n">
@@ -9479,19 +9479,19 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2187</v>
+        <v>20295</v>
       </c>
       <c r="J72" t="n">
-        <v>3808</v>
+        <v>21917</v>
       </c>
       <c r="K72" t="n">
-        <v>2634</v>
+        <v>20743</v>
       </c>
       <c r="L72" t="n">
-        <v>0.96</v>
+        <v>7.6</v>
       </c>
       <c r="M72" t="n">
-        <v>0.955</v>
+        <v>0.9562499999999999</v>
       </c>
       <c r="N72" t="n">
         <v>26.1225</v>
@@ -9503,7 +9503,7 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -9521,10 +9521,10 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>-1.32</v>
+        <v>11.95</v>
       </c>
       <c r="X72" t="n">
-        <v>-0.5789473684210527</v>
+        <v>-2.747126436781609</v>
       </c>
       <c r="Y72" t="n">
         <v>-0.03999999999999915</v>
@@ -9533,10 +9533,10 @@
         <v>-0.001606425702811221</v>
       </c>
       <c r="AA72" t="n">
-        <v>-0.3400000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="AB72" t="n">
-        <v>-0.2615384615384616</v>
+        <v>4.846153846153846</v>
       </c>
       <c r="AC72" t="n">
         <v>0.8399999999999999</v>
@@ -9545,10 +9545,10 @@
         <v>0.03497085761865115</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -9557,11 +9557,11 @@
         <v>1</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>EPS衰退 / 毛利率成長</t>
+          <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
       <c r="AK72" t="n">
@@ -9618,7 +9618,7 @@
         <v>1.25</v>
       </c>
       <c r="M73" t="n">
-        <v>1.24875</v>
+        <v>1.25</v>
       </c>
       <c r="N73" t="n">
         <v>25.61125</v>
@@ -9648,10 +9648,10 @@
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>0.29</v>
+        <v>-6.35</v>
       </c>
       <c r="X73" t="n">
-        <v>0.3020833333333335</v>
+        <v>-0.8355263157894737</v>
       </c>
       <c r="Y73" t="n">
         <v>-1.939999999999998</v>
@@ -9672,7 +9672,7 @@
         <v>-0.2531769305962854</v>
       </c>
       <c r="AE73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
         <v>1</v>
@@ -9745,7 +9745,7 @@
         <v>0.99</v>
       </c>
       <c r="M74" t="n">
-        <v>1.065</v>
+        <v>1.06625</v>
       </c>
       <c r="N74" t="n">
         <v>25.5125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>13715</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9998</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3717</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2968</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>21.64%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5523</v>
+      </c>
+      <c r="J75" t="n">
+        <v>8491</v>
+      </c>
+      <c r="K75" t="n">
+        <v>7375</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.21375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.4275</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.747474747474748</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.360000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09539207760711421</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.625287356321839</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.200000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08835341365461868</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
